--- a/result/Table202604.xlsx
+++ b/result/Table202604.xlsx
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I28" t="n">
         <v>37.03</v>
       </c>
       <c r="J28" t="n">
-        <v>27.46</v>
+        <v>26.58</v>
       </c>
       <c r="K28" t="n">
-        <v>-25.84</v>
+        <v>-28.22</v>
       </c>
       <c r="L28" t="n">
-        <v>-25843.91</v>
+        <v>-28220.36</v>
       </c>
     </row>
     <row r="29">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I29" t="n">
         <v>47.26</v>
       </c>
       <c r="J29" t="n">
-        <v>23.71</v>
+        <v>25.03</v>
       </c>
       <c r="K29" t="n">
-        <v>-49.83</v>
+        <v>-47.04</v>
       </c>
       <c r="L29" t="n">
-        <v>-49830.72</v>
+        <v>-47037.66</v>
       </c>
     </row>
     <row r="30">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I31" t="n">
         <v>127.39</v>
       </c>
       <c r="J31" t="n">
-        <v>125.32</v>
+        <v>128.71</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.62</v>
+        <v>1.04</v>
       </c>
       <c r="L31" t="n">
-        <v>-1624.93</v>
+        <v>1036.19</v>
       </c>
     </row>
     <row r="32">

--- a/result/Table202604.xlsx
+++ b/result/Table202604.xlsx
@@ -616,24 +616,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
         <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>4.87</v>
+        <v>4.55</v>
       </c>
       <c r="K4" t="n">
-        <v>10.68</v>
+        <v>3.41</v>
       </c>
       <c r="L4" t="n">
-        <v>10681.82</v>
+        <v>3409.09</v>
       </c>
     </row>
     <row r="5">
@@ -762,24 +762,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
         <v>8.890000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>9.4</v>
+        <v>8.75</v>
       </c>
       <c r="K7" t="n">
-        <v>5.74</v>
+        <v>-1.57</v>
       </c>
       <c r="L7" t="n">
-        <v>5736.78</v>
+        <v>-1574.8</v>
       </c>
     </row>
     <row r="8">
@@ -808,24 +808,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="I8" t="n">
         <v>8.67</v>
       </c>
       <c r="J8" t="n">
-        <v>8.34</v>
+        <v>8.83</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.81</v>
+        <v>1.85</v>
       </c>
       <c r="L8" t="n">
-        <v>-3806.23</v>
+        <v>1845.44</v>
       </c>
     </row>
     <row r="9">
@@ -1204,24 +1204,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
         <v>25.68</v>
       </c>
       <c r="J16" t="n">
-        <v>23.37</v>
+        <v>23.01</v>
       </c>
       <c r="K16" t="n">
-        <v>-9</v>
+        <v>-10.4</v>
       </c>
       <c r="L16" t="n">
-        <v>-8995.33</v>
+        <v>-10397.2</v>
       </c>
     </row>
     <row r="17">
@@ -1450,24 +1450,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I21" t="n">
         <v>71.98999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>79.92</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>11.02</v>
+        <v>9.06</v>
       </c>
       <c r="L21" t="n">
-        <v>11015.42</v>
+        <v>9056.809999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1592,24 +1592,24 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="I24" t="n">
         <v>65.34</v>
       </c>
       <c r="J24" t="n">
-        <v>76.51000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="K24" t="n">
-        <v>17.1</v>
+        <v>47.23</v>
       </c>
       <c r="L24" t="n">
-        <v>17095.19</v>
+        <v>47229.87</v>
       </c>
     </row>
     <row r="25">
@@ -1684,24 +1684,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
         <v>6.97</v>
       </c>
       <c r="J26" t="n">
-        <v>7.24</v>
+        <v>6.52</v>
       </c>
       <c r="K26" t="n">
-        <v>3.87</v>
+        <v>-6.46</v>
       </c>
       <c r="L26" t="n">
-        <v>3873.74</v>
+        <v>-6456.24</v>
       </c>
     </row>
     <row r="27">

--- a/result/Table202604.xlsx
+++ b/result/Table202604.xlsx
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I28" t="n">
         <v>37.03</v>
       </c>
       <c r="J28" t="n">
-        <v>26.58</v>
+        <v>26.47</v>
       </c>
       <c r="K28" t="n">
-        <v>-28.22</v>
+        <v>-28.52</v>
       </c>
       <c r="L28" t="n">
-        <v>-28220.36</v>
+        <v>-28517.42</v>
       </c>
     </row>
     <row r="29">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I29" t="n">
         <v>47.26</v>
       </c>
       <c r="J29" t="n">
-        <v>25.03</v>
+        <v>24.56</v>
       </c>
       <c r="K29" t="n">
-        <v>-47.04</v>
+        <v>-48.03</v>
       </c>
       <c r="L29" t="n">
-        <v>-47037.66</v>
+        <v>-48032.16</v>
       </c>
     </row>
     <row r="30">
@@ -1930,28 +1930,28 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>0940</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I31" t="n">
         <v>127.39</v>
       </c>
       <c r="J31" t="n">
-        <v>128.71</v>
+        <v>137.3</v>
       </c>
       <c r="K31" t="n">
-        <v>1.04</v>
+        <v>7.78</v>
       </c>
       <c r="L31" t="n">
-        <v>1036.19</v>
+        <v>7779.26</v>
       </c>
     </row>
     <row r="32">

--- a/result/Table202604.xlsx
+++ b/result/Table202604.xlsx
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I28" t="n">
         <v>37.03</v>
       </c>
       <c r="J28" t="n">
-        <v>26.47</v>
+        <v>27.04</v>
       </c>
       <c r="K28" t="n">
-        <v>-28.52</v>
+        <v>-26.98</v>
       </c>
       <c r="L28" t="n">
-        <v>-28517.42</v>
+        <v>-26978.13</v>
       </c>
     </row>
     <row r="29">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I29" t="n">
         <v>47.26</v>
       </c>
       <c r="J29" t="n">
-        <v>24.56</v>
+        <v>23.45</v>
       </c>
       <c r="K29" t="n">
-        <v>-48.03</v>
+        <v>-50.38</v>
       </c>
       <c r="L29" t="n">
-        <v>-48032.16</v>
+        <v>-50380.87</v>
       </c>
     </row>
     <row r="30">

--- a/result/Table202604.xlsx
+++ b/result/Table202604.xlsx
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I28" t="n">
         <v>37.03</v>
       </c>
       <c r="J28" t="n">
-        <v>27.04</v>
+        <v>26.82</v>
       </c>
       <c r="K28" t="n">
-        <v>-26.98</v>
+        <v>-27.57</v>
       </c>
       <c r="L28" t="n">
-        <v>-26978.13</v>
+        <v>-27572.24</v>
       </c>
     </row>
     <row r="29">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I29" t="n">
         <v>47.26</v>
       </c>
       <c r="J29" t="n">
-        <v>23.45</v>
+        <v>24.93</v>
       </c>
       <c r="K29" t="n">
-        <v>-50.38</v>
+        <v>-47.25</v>
       </c>
       <c r="L29" t="n">
-        <v>-50380.87</v>
+        <v>-47249.26</v>
       </c>
     </row>
     <row r="30">
